--- a/data_output/montecarlo_intervals.xlsx
+++ b/data_output/montecarlo_intervals.xlsx
@@ -416,13 +416,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.8644419781172732</v>
+        <v>2.931372761679691</v>
       </c>
       <c r="E2">
-        <v>0.05518429495425125</v>
+        <v>0.4293409017528119</v>
       </c>
       <c r="F2">
-        <v>9.557031053424733</v>
+        <v>20.20052699957823</v>
       </c>
       <c r="G2">
         <v>0.66</v>
@@ -453,13 +453,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.8644419781172732</v>
+        <v>2.931372761679691</v>
       </c>
       <c r="E3">
-        <v>0.005605890021192486</v>
+        <v>0.0488906512416263</v>
       </c>
       <c r="F3">
-        <v>122.4069427526164</v>
+        <v>229.4861787354605</v>
       </c>
       <c r="G3">
         <v>0.95</v>
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.4345922762804048</v>
+        <v>1.473727553004054</v>
       </c>
       <c r="E4">
-        <v>0.02774352584233679</v>
+        <v>0.2158481939984211</v>
       </c>
       <c r="F4">
-        <v>4.804731821372634</v>
+        <v>10.15567641674557</v>
       </c>
       <c r="G4">
         <v>0.66</v>
@@ -527,13 +527,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.4345922762804048</v>
+        <v>1.473727553004054</v>
       </c>
       <c r="E5">
-        <v>0.002818322763771584</v>
+        <v>0.02457943962671288</v>
       </c>
       <c r="F5">
-        <v>61.53925101976926</v>
+        <v>115.3726025762315</v>
       </c>
       <c r="G5">
         <v>0.95</v>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.4175177323823958</v>
+        <v>0.5195050011779367</v>
       </c>
       <c r="E6">
-        <v>0.05220948381764941</v>
+        <v>0.04271792363755121</v>
       </c>
       <c r="F6">
-        <v>3.807547624993124</v>
+        <v>5.46722738052997</v>
       </c>
       <c r="G6">
         <v>0.66</v>
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.4175177323823958</v>
+        <v>0.5195050011779367</v>
       </c>
       <c r="E7">
-        <v>0.007757085443777916</v>
+        <v>0.002916012995041242</v>
       </c>
       <c r="F7">
-        <v>46.25727920859265</v>
+        <v>66.46951163905601</v>
       </c>
       <c r="G7">
         <v>0.95</v>
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.2099041766790299</v>
+        <v>0.26117757665205</v>
       </c>
       <c r="E8">
-        <v>0.02624795994423472</v>
+        <v>0.02147614315543722</v>
       </c>
       <c r="F8">
-        <v>1.914218456854399</v>
+        <v>2.748611072106838</v>
       </c>
       <c r="G8">
         <v>0.66</v>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.2099041766790299</v>
+        <v>0.26117757665205</v>
       </c>
       <c r="E9">
-        <v>0.003899821509889346</v>
+        <v>0.001466005535661632</v>
       </c>
       <c r="F9">
-        <v>23.25552989638972</v>
+        <v>33.41709113823863</v>
       </c>
       <c r="G9">
         <v>0.95</v>
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>1.760895916725645</v>
+        <v>11.89457941527705</v>
       </c>
       <c r="E10">
-        <v>0.08844403277361529</v>
+        <v>1.467435336452066</v>
       </c>
       <c r="F10">
-        <v>27.70809453852019</v>
+        <v>112.0390509851856</v>
       </c>
       <c r="G10">
         <v>0.66</v>
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>1.760895916725645</v>
+        <v>11.89457941527705</v>
       </c>
       <c r="E11">
-        <v>0.00723628437258984</v>
+        <v>0.1261786766871902</v>
       </c>
       <c r="F11">
-        <v>847.7692770298842</v>
+        <v>2019.429202615591</v>
       </c>
       <c r="G11">
         <v>0.95</v>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.8852783461643141</v>
+        <v>5.979918229725319</v>
       </c>
       <c r="E12">
-        <v>0.04446463094055073</v>
+        <v>0.7377430519419863</v>
       </c>
       <c r="F12">
-        <v>13.93005451113634</v>
+        <v>56.32686453519557</v>
       </c>
       <c r="G12">
         <v>0.66</v>
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.8852783461643141</v>
+        <v>5.979918229725319</v>
       </c>
       <c r="E13">
-        <v>0.00363799234292796</v>
+        <v>0.06343546438937045</v>
       </c>
       <c r="F13">
-        <v>426.2101901476925</v>
+        <v>1015.254182661604</v>
       </c>
       <c r="G13">
         <v>0.95</v>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.006518912678380082</v>
+        <v>0.008147575007839546</v>
       </c>
       <c r="E14">
-        <v>0.0005811392548887017</v>
+        <v>0.0007589749966563198</v>
       </c>
       <c r="F14">
-        <v>0.08868034695587994</v>
+        <v>0.07475505848792915</v>
       </c>
       <c r="G14">
         <v>0.66</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.006518912678380082</v>
+        <v>0.008147575007839546</v>
       </c>
       <c r="E15">
-        <v>3.722011754928081E-05</v>
+        <v>5.848844646090361E-05</v>
       </c>
       <c r="F15">
-        <v>1.299828927812281</v>
+        <v>1.470230495862668</v>
       </c>
       <c r="G15">
         <v>0.95</v>
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.003277338643295324</v>
+        <v>0.00409613746030038</v>
       </c>
       <c r="E16">
-        <v>0.0002921637750263398</v>
+        <v>0.0003815694746282147</v>
       </c>
       <c r="F16">
-        <v>0.0445834362750758</v>
+        <v>0.03758259299542772</v>
       </c>
       <c r="G16">
         <v>0.66</v>
@@ -971,13 +971,13 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.003277338643295324</v>
+        <v>0.00409613746030038</v>
       </c>
       <c r="E17">
-        <v>1.871215884771824E-05</v>
+        <v>2.940466535291314E-05</v>
       </c>
       <c r="F17">
-        <v>0.6534800794188428</v>
+        <v>0.7391482991668679</v>
       </c>
       <c r="G17">
         <v>0.95</v>
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.00316449145177721</v>
+        <v>0.006005877667645365</v>
       </c>
       <c r="E18">
-        <v>0.0005547706952731501</v>
+        <v>0.001356275383595973</v>
       </c>
       <c r="F18">
-        <v>0.02242675958410079</v>
+        <v>0.03972504598263439</v>
       </c>
       <c r="G18">
         <v>0.66</v>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.00316449145177721</v>
+        <v>0.006005877667645365</v>
       </c>
       <c r="E19">
-        <v>9.881077886554984E-05</v>
+        <v>0.0003256173777949868</v>
       </c>
       <c r="F19">
-        <v>0.1353727277278675</v>
+        <v>0.178394400759981</v>
       </c>
       <c r="G19">
         <v>0.95</v>
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.001590926375756324</v>
+        <v>0.003019413809968344</v>
       </c>
       <c r="E20">
-        <v>0.0002789071625113892</v>
+        <v>0.0006818581479624646</v>
       </c>
       <c r="F20">
-        <v>0.01127489958143322</v>
+        <v>0.01997149443914986</v>
       </c>
       <c r="G20">
         <v>0.66</v>
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.001590926375756324</v>
+        <v>0.003019413809968344</v>
       </c>
       <c r="E21">
-        <v>4.967644144462555E-05</v>
+        <v>0.0001637019036495495</v>
       </c>
       <c r="F21">
-        <v>0.06805771049859871</v>
+        <v>0.08968656157908272</v>
       </c>
       <c r="G21">
         <v>0.95</v>
@@ -1156,13 +1156,13 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0002752506725657662</v>
+        <v>0.0002987140470927838</v>
       </c>
       <c r="E22">
-        <v>6.006510785768769E-05</v>
+        <v>8.627855598860717E-05</v>
       </c>
       <c r="F22">
-        <v>0.0009643740790719834</v>
+        <v>0.001287715097987189</v>
       </c>
       <c r="G22">
         <v>0.66</v>
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.0002752506725657662</v>
+        <v>0.0002987140470927838</v>
       </c>
       <c r="E23">
-        <v>1.50684622903232E-05</v>
+        <v>2.889232786740623E-05</v>
       </c>
       <c r="F23">
-        <v>0.005079902051081006</v>
+        <v>0.005246039247349243</v>
       </c>
       <c r="G23">
         <v>0.95</v>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.0001383803880031383</v>
+        <v>0.0001501764386381676</v>
       </c>
       <c r="E24">
-        <v>3.019732105763052E-05</v>
+        <v>4.337595233741449E-05</v>
       </c>
       <c r="F24">
-        <v>0.0004848324547154909</v>
+        <v>0.0006473899345491702</v>
       </c>
       <c r="G24">
         <v>0.66</v>
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.0001383803880031383</v>
+        <v>0.0001501764386381676</v>
       </c>
       <c r="E25">
-        <v>7.575566079125082E-06</v>
+        <v>1.45254196959329E-05</v>
       </c>
       <c r="F25">
-        <v>0.002553885918947459</v>
+        <v>0.002637410255026453</v>
       </c>
       <c r="G25">
         <v>0.95</v>
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="D26">
-        <v>2.611044921665882</v>
+        <v>5.252500154068264</v>
       </c>
       <c r="E26">
-        <v>0.2766024166312035</v>
+        <v>1.015728794394724</v>
       </c>
       <c r="F26">
-        <v>30.85093357966093</v>
+        <v>35.03513850465198</v>
       </c>
       <c r="G26">
         <v>0.66</v>
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="D27">
-        <v>2.611044921665882</v>
+        <v>5.252500154068264</v>
       </c>
       <c r="E27">
-        <v>0.03319983611373369</v>
+        <v>0.1885613571258798</v>
       </c>
       <c r="F27">
-        <v>301.4343460578142</v>
+        <v>182.6365477501888</v>
       </c>
       <c r="G27">
         <v>0.95</v>
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="D28">
-        <v>1.312684928199107</v>
+        <v>2.640658431571477</v>
       </c>
       <c r="E28">
-        <v>0.1390599680619716</v>
+        <v>0.510650685660789</v>
       </c>
       <c r="F28">
-        <v>15.51009528593427</v>
+        <v>17.61367561730135</v>
       </c>
       <c r="G28">
         <v>0.66</v>
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="D29">
-        <v>1.312684928199107</v>
+        <v>2.640658431571477</v>
       </c>
       <c r="E29">
-        <v>0.01669098992650551</v>
+        <v>0.09479792916852212</v>
       </c>
       <c r="F29">
-        <v>151.5440502874198</v>
+        <v>91.81927188637924</v>
       </c>
       <c r="G29">
         <v>0.95</v>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="D30">
-        <v>2.021809529260511</v>
+        <v>7.780142588211151</v>
       </c>
       <c r="E30">
-        <v>0.2384749136905382</v>
+        <v>1.606632869997942</v>
       </c>
       <c r="F30">
-        <v>22.73548774024201</v>
+        <v>66.09956124259737</v>
       </c>
       <c r="G30">
         <v>0.66</v>
@@ -1489,13 +1489,13 @@
         </is>
       </c>
       <c r="D31">
-        <v>2.021809529260511</v>
+        <v>7.780142588211151</v>
       </c>
       <c r="E31">
-        <v>0.02089075263498313</v>
+        <v>0.2358625706551428</v>
       </c>
       <c r="F31">
-        <v>317.0318070703485</v>
+        <v>407.0837080080145</v>
       </c>
       <c r="G31">
         <v>0.95</v>
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="D32">
-        <v>1.016450875558402</v>
+        <v>3.911413331130595</v>
       </c>
       <c r="E32">
-        <v>0.1198916274314526</v>
+        <v>0.8077236573356236</v>
       </c>
       <c r="F32">
-        <v>11.43011054472018</v>
+        <v>33.23110111348537</v>
       </c>
       <c r="G32">
         <v>0.66</v>
@@ -1563,13 +1563,13 @@
         </is>
       </c>
       <c r="D33">
-        <v>1.016450875558402</v>
+        <v>3.911413331130595</v>
       </c>
       <c r="E33">
-        <v>0.0105026826214778</v>
+        <v>0.1185782898854783</v>
       </c>
       <c r="F33">
-        <v>159.3855668463398</v>
+        <v>204.6585424798397</v>
       </c>
       <c r="G33">
         <v>0.95</v>
@@ -1600,13 +1600,13 @@
         </is>
       </c>
       <c r="D34">
-        <v>1.638737549454963</v>
+        <v>5.775999661425217</v>
       </c>
       <c r="E34">
-        <v>0.1725374620037724</v>
+        <v>1.2609772338771</v>
       </c>
       <c r="F34">
-        <v>22.45262072709714</v>
+        <v>37.87448072740241</v>
       </c>
       <c r="G34">
         <v>0.66</v>
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="D35">
-        <v>1.638737549454963</v>
+        <v>5.775999661425217</v>
       </c>
       <c r="E35">
-        <v>0.01132644969159087</v>
+        <v>0.2909077652714603</v>
       </c>
       <c r="F35">
-        <v>498.4890167741485</v>
+        <v>237.8127769356774</v>
       </c>
       <c r="G35">
         <v>0.95</v>
@@ -1674,13 +1674,13 @@
         </is>
       </c>
       <c r="D36">
-        <v>0.8238640647633929</v>
+        <v>2.903844218811282</v>
       </c>
       <c r="E36">
-        <v>0.08674202578543767</v>
+        <v>0.6339476567322281</v>
       </c>
       <c r="F36">
-        <v>11.28790109372265</v>
+        <v>19.04113544799084</v>
       </c>
       <c r="G36">
         <v>0.66</v>
@@ -1711,13 +1711,13 @@
         </is>
       </c>
       <c r="D37">
-        <v>0.8238640647633929</v>
+        <v>2.903844218811282</v>
       </c>
       <c r="E37">
-        <v>0.005694294907293563</v>
+        <v>0.1462518839868489</v>
       </c>
       <c r="F37">
-        <v>250.6119346176268</v>
+        <v>119.5587427187845</v>
       </c>
       <c r="G37">
         <v>0.95</v>
